--- a/querys.xlsx
+++ b/querys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\v6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78C2DF15-CD1E-4BF7-9BD3-E178FF77E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98B3717-5F1B-409E-B755-1E304CA00D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{06A852CD-5681-4B46-84CE-8DF3612BBE96}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="134">
   <si>
     <t>star_border</t>
   </si>
@@ -332,6 +332,111 @@
   </si>
   <si>
     <t>&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#707070;'&gt;Rascunho&lt;/div&gt;"</t>
+  </si>
+  <si>
+    <t>&lt;div style='background-color:#fff;color:#000;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400'&gt;Ações&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#b70505;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Apagar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:rgba(0,0,0,.26);border:1px solid currentColor;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;readonly/inativo&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='background-color:#ff7043;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;';font-size:14px;font-weight:400'&gt;Introduza&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#1a237e;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#1a237e;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#1976d2;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);background-color: rgba(0,0,0,.12);color: #fff !important;box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='background-color: rgba(0,0,0,.12);color: rgba(0,0,0,.26);box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#1a237e;'&gt;@FTeixeira&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#00bfa5;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#004d40;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#004d40;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#00bfa5;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#004d40;'&gt;@FTeixeira&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='background-color:#d32f2f;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;';font-size:14px;font-weight:400'&gt;Introduza&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='background-color:#303030;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400'&gt;Ações&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#616161;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:rgba(0,0,0,.87);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#e0e0e0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#e0e0e0;border:1px solid hsla(0,0%,100%,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#ff7171;border:1px solid hsla(0,0%,100%,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Apagar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:hsla(0,0%,100%,.3);border:1px solid hsla(0,0%,100%,.3);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;readonly/inativo&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#616161;border:1px solid hsla(0,0%,100%,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='background-color: rgba(0,0,0,.12);color: #fff!important;box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='background-color: rgba(0,0,0,.12);color: hsla(0,0%,100%,.3);box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:rgba(0,0,0,.87);background-color:#e0e0e0;'&gt;@FTeixeira&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#212121;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#212121;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#616161;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#212121;'&gt;@FTeixeira&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>&lt;div style="background-color:#ff8f00;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400"&gt;Introduza&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="background-color:#fff;color:#000;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400"&gt;Ações&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#1976d2;font-size:14px;font-weight:400;line-height:34px"&gt;Processar&lt;/div&gt;</t>
   </si>
 </sst>
 </file>
@@ -1961,13 +2066,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF1DDB85-0961-4A3F-87F9-EB3D9CFF674B}">
-  <dimension ref="B1:E61"/>
+  <dimension ref="B1:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="166.28515625" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>91</v>
       </c>
@@ -1981,7 +2086,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>1</v>
       </c>
@@ -1991,8 +2096,20 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" t="str">
+        <f>"INSERT INTO buttons (id, theme, subid, code)
+VALUES ('"&amp;B2&amp;"', '"&amp;C2&amp;"', '"&amp;D2&amp;"', '"&amp;E2&amp;"');"</f>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('1', 'horizon', '1', '&lt;div style="background-color:#ff8f00;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400"&gt;Introduza&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>2</v>
       </c>
@@ -2002,8 +2119,20 @@
       <c r="D3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G61" si="0">"INSERT INTO buttons (id, theme, subid, code)
+VALUES ('"&amp;B3&amp;"', '"&amp;C3&amp;"', '"&amp;D3&amp;"', '"&amp;E3&amp;"');"</f>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('2', 'horizon', '2', '&lt;div style="background-color:#fff;color:#000;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400"&gt;Ações&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>3</v>
       </c>
@@ -2013,8 +2142,19 @@
       <c r="D4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('3', 'horizon', '3', '&lt;div style="box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#1976d2;font-size:14px;font-weight:400;line-height:34px"&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>4</v>
       </c>
@@ -2024,8 +2164,19 @@
       <c r="D5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('4', 'horizon', '4', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#1a237e;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>5</v>
       </c>
@@ -2035,8 +2186,19 @@
       <c r="D6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('5', 'horizon', '5', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#1a237e;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>6</v>
       </c>
@@ -2046,8 +2208,19 @@
       <c r="D7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('6', 'horizon', '6', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#b70505;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Apagar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>7</v>
       </c>
@@ -2057,8 +2230,19 @@
       <c r="D8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('7', 'horizon', '7', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:rgba(0,0,0,.26);border:1px solid currentColor;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;readonly/inativo&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>8</v>
       </c>
@@ -2068,8 +2252,19 @@
       <c r="D9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('8', 'horizon', '8', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#1976d2;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>9</v>
       </c>
@@ -2079,8 +2274,19 @@
       <c r="D10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('9', 'horizon', '9', '&lt;div style='box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);background-color: rgba(0,0,0,.12);color: #fff !important;box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>10</v>
       </c>
@@ -2090,8 +2296,19 @@
       <c r="D11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('10', 'horizon', '10', '&lt;div style='background-color: rgba(0,0,0,.12);color: rgba(0,0,0,.26);box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>11</v>
       </c>
@@ -2104,8 +2321,16 @@
       <c r="E12" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('11', 'horizon', '11', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#139b25;'&gt;Assinado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>12</v>
       </c>
@@ -2118,8 +2343,16 @@
       <c r="E13" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('12', 'horizon', '12', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#ff8f00;'&gt;Em edição&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>13</v>
       </c>
@@ -2132,8 +2365,16 @@
       <c r="E14" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('13', 'horizon', '13', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#b70505;'&gt;Anulado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>14</v>
       </c>
@@ -2146,8 +2387,16 @@
       <c r="E15" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('14', 'horizon', '14', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#707070;'&gt;Rascunho&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>15</v>
       </c>
@@ -2157,8 +2406,19 @@
       <c r="D16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('15', 'horizon', '15', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#1a237e;'&gt;@FTeixeira&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>16</v>
       </c>
@@ -2168,8 +2428,19 @@
       <c r="D17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('16', 'forest', '1', '&lt;div style='background-color:#ff7043;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;';font-size:14px;font-weight:400'&gt;Introduza&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>17</v>
       </c>
@@ -2179,8 +2450,19 @@
       <c r="D18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('17', 'forest', '2', '&lt;div style='background-color:#fff;color:#000;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400'&gt;Ações&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>18</v>
       </c>
@@ -2190,8 +2472,19 @@
       <c r="D19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('18', 'forest', '3', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#00bfa5;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>19</v>
       </c>
@@ -2201,8 +2494,19 @@
       <c r="D20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('19', 'forest', '4', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#004d40;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>20</v>
       </c>
@@ -2212,8 +2516,19 @@
       <c r="D21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('20', 'forest', '5', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#004d40;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>21</v>
       </c>
@@ -2223,8 +2538,19 @@
       <c r="D22">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('21', 'forest', '6', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#b70505;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Apagar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>22</v>
       </c>
@@ -2234,8 +2560,19 @@
       <c r="D23">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('22', 'forest', '7', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:rgba(0,0,0,.26);border:1px solid currentColor;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;readonly/inativo&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>23</v>
       </c>
@@ -2245,8 +2582,19 @@
       <c r="D24">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('23', 'forest', '8', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#00bfa5;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>24</v>
       </c>
@@ -2256,8 +2604,19 @@
       <c r="D25">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" t="s">
+        <v>129</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('24', 'forest', '9', '&lt;div style='box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);background-color: rgba(0,0,0,.12);color: #fff !important;box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>25</v>
       </c>
@@ -2267,8 +2626,19 @@
       <c r="D26">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('25', 'forest', '10', '&lt;div style='background-color: rgba(0,0,0,.12);color: rgba(0,0,0,.26);box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>26</v>
       </c>
@@ -2281,8 +2651,16 @@
       <c r="E27" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('26', 'forest', '11', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#139b25;'&gt;Assinado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>27</v>
       </c>
@@ -2295,8 +2673,16 @@
       <c r="E28" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('27', 'forest', '12', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#ff8f00;'&gt;Em edição&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>28</v>
       </c>
@@ -2309,8 +2695,16 @@
       <c r="E29" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('28', 'forest', '13', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#b70505;'&gt;Anulado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>29</v>
       </c>
@@ -2323,8 +2717,16 @@
       <c r="E30" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('29', 'forest', '14', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#707070;'&gt;Rascunho&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>30</v>
       </c>
@@ -2334,8 +2736,19 @@
       <c r="D31">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" t="s">
+        <v>129</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('30', 'forest', '15', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#004d40;'&gt;@FTeixeira&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>31</v>
       </c>
@@ -2345,8 +2758,19 @@
       <c r="D32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('31', 'dark', '1', '&lt;div style='background-color:#d32f2f;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;';font-size:14px;font-weight:400'&gt;Introduza&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>32</v>
       </c>
@@ -2356,8 +2780,19 @@
       <c r="D33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('32', 'dark', '2', '&lt;div style='background-color:#303030;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400'&gt;Ações&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>33</v>
       </c>
@@ -2367,8 +2802,19 @@
       <c r="D34">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('33', 'dark', '3', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#616161;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>34</v>
       </c>
@@ -2378,8 +2824,19 @@
       <c r="D35">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('34', 'dark', '4', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:rgba(0,0,0,.87);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#e0e0e0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>35</v>
       </c>
@@ -2389,8 +2846,19 @@
       <c r="D36">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>118</v>
+      </c>
+      <c r="F36" t="s">
+        <v>129</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('35', 'dark', '5', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#e0e0e0;border:1px solid hsla(0,0%,100%,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>36</v>
       </c>
@@ -2400,8 +2868,19 @@
       <c r="D37">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F37" t="s">
+        <v>129</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('36', 'dark', '6', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#ff7171;border:1px solid hsla(0,0%,100%,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Apagar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>37</v>
       </c>
@@ -2411,8 +2890,19 @@
       <c r="D38">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>120</v>
+      </c>
+      <c r="F38" t="s">
+        <v>129</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('37', 'dark', '7', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:hsla(0,0%,100%,.3);border:1px solid hsla(0,0%,100%,.3);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;readonly/inativo&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>38</v>
       </c>
@@ -2422,8 +2912,19 @@
       <c r="D39">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('38', 'dark', '8', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#616161;border:1px solid hsla(0,0%,100%,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>39</v>
       </c>
@@ -2433,8 +2934,19 @@
       <c r="D40">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" t="s">
+        <v>129</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('39', 'dark', '9', '&lt;div style='background-color: rgba(0,0,0,.12);color: #fff!important;box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>40</v>
       </c>
@@ -2444,8 +2956,19 @@
       <c r="D41">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" t="s">
+        <v>129</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('40', 'dark', '10', '&lt;div style='background-color: rgba(0,0,0,.12);color: hsla(0,0%,100%,.3);box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>41</v>
       </c>
@@ -2458,8 +2981,16 @@
       <c r="E42" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>129</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('41', 'dark', '11', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#139b25;'&gt;Assinado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>42</v>
       </c>
@@ -2472,8 +3003,16 @@
       <c r="E43" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('42', 'dark', '12', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#ff8f00;'&gt;Em edição&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>43</v>
       </c>
@@ -2486,8 +3025,16 @@
       <c r="E44" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F44" t="s">
+        <v>129</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('43', 'dark', '13', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#b70505;'&gt;Anulado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>44</v>
       </c>
@@ -2500,8 +3047,16 @@
       <c r="E45" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F45" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('44', 'dark', '14', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#707070;'&gt;Rascunho&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>45</v>
       </c>
@@ -2511,8 +3066,19 @@
       <c r="D46">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('45', 'dark', '15', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:rgba(0,0,0,.87);background-color:#e0e0e0;'&gt;@FTeixeira&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>46</v>
       </c>
@@ -2522,8 +3088,19 @@
       <c r="D47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('46', 'light', '1', '&lt;div style='background-color:#d32f2f;color:#fff;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;';font-size:14px;font-weight:400'&gt;Introduza&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>47</v>
       </c>
@@ -2533,8 +3110,19 @@
       <c r="D48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>99</v>
+      </c>
+      <c r="F48" t="s">
+        <v>129</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('47', 'light', '2', '&lt;div style='background-color:#fff;color:#000;box-shadow:0 3px 1px -2px rgba(0,0,0,.2),0 2px 2px 0 rgba(0,0,0,.14),0 1px 5px 0 rgba(0,0,0,.12);box-sizing:border-box;outline:0;border:none;display:inline-block;text-align:center;margin:0;min-width:64px;line-height:36px;padding:0 16px;border-radius:4px;font-size:14px;font-weight:400'&gt;Ações&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>48</v>
       </c>
@@ -2544,8 +3132,19 @@
       <c r="D49">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>116</v>
+      </c>
+      <c r="F49" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('48', 'light', '3', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#616161;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>49</v>
       </c>
@@ -2555,8 +3154,19 @@
       <c r="D50">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>125</v>
+      </c>
+      <c r="F50" t="s">
+        <v>129</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('49', 'light', '4', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);border:0;color:#fff;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:#212121;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>50</v>
       </c>
@@ -2566,8 +3176,19 @@
       <c r="D51">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>126</v>
+      </c>
+      <c r="F51" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('50', 'light', '5', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#212121;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Introduzir&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>51</v>
       </c>
@@ -2577,8 +3198,19 @@
       <c r="D52">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" t="s">
+        <v>129</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('51', 'light', '6', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#b70505;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Apagar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>52</v>
       </c>
@@ -2588,8 +3220,19 @@
       <c r="D53">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F53" t="s">
+        <v>129</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('52', 'light', '7', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:rgba(0,0,0,.26);border:1px solid currentColor;box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;readonly/inativo&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>53</v>
       </c>
@@ -2599,8 +3242,19 @@
       <c r="D54">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>127</v>
+      </c>
+      <c r="F54" t="s">
+        <v>129</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('53', 'light', '8', '&lt;div style='box-shadow:0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);color:#616161;border:1px solid rgba(0,0,0,.12);box-sizing:border-box;outline:0;display:inline-block;text-align:center;margin:0;min-width:64px;padding:0 16px;border-radius:4px;overflow:visible;background:0 0;font-size:14px;font-weight:400;line-height:34px'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>54</v>
       </c>
@@ -2610,8 +3264,19 @@
       <c r="D55">
         <v>9</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>106</v>
+      </c>
+      <c r="F55" t="s">
+        <v>129</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('54', 'light', '9', '&lt;div style='box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);background-color: rgba(0,0,0,.12);color: #fff !important;box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>55</v>
       </c>
@@ -2621,8 +3286,19 @@
       <c r="D56">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" t="s">
+        <v>129</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('55', 'light', '10', '&lt;div style='background-color: rgba(0,0,0,.12);color: rgba(0,0,0,.26);box-shadow: 0 0 0 0 rgba(0,0,0,.2),0 0 0 0 rgba(0,0,0,.14),0 0 0 0 rgba(0,0,0,.12);box-sizing: border-box;position: relative;-webkit-user-select: none;-moz-user-select: none;-ms-user-select: none;user-select: none;cursor: pointer;outline: none;border: none;-webkit-tap-highlight-color: transparent;display: inline-block;white-space: nowrap;text-decoration: none;vertical-align: baseline;text-align: center;margin: 0;min-width: 64px;line-height: 36px;padding: 0 16px;border-radius: 4px;overflow: visible;font-size: 14px;font-weight: 400;'&gt;Processar&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>56</v>
       </c>
@@ -2635,8 +3311,16 @@
       <c r="E57" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F57" t="s">
+        <v>129</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('56', 'light', '11', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#139b25;'&gt;Assinado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>57</v>
       </c>
@@ -2649,8 +3333,16 @@
       <c r="E58" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F58" t="s">
+        <v>129</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('57', 'light', '12', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#ff8f00;'&gt;Em edição&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>58</v>
       </c>
@@ -2663,8 +3355,16 @@
       <c r="E59" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F59" t="s">
+        <v>129</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('58', 'light', '13', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#b70505;'&gt;Anulado&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>59</v>
       </c>
@@ -2677,8 +3377,16 @@
       <c r="E60" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F60" t="s">
+        <v>129</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('59', 'light', '14', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#707070;'&gt;Rascunho&lt;/div&gt;"');</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>60</v>
       </c>
@@ -2687,6 +3395,22 @@
       </c>
       <c r="D61">
         <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61" t="s">
+        <v>129</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="0"/>
+        <v>INSERT INTO buttons (id, theme, subid, code)
+VALUES ('60', 'light', '15', '&lt;div style='display:inline-flex;padding:7px 12px;border-radius:16px;align-items:center;min-height:32px;height:1px;border:none;-webkit-appearance:none;-moz-appearance:none;position:relative;box-sizing:border-box;font-size:14px;font-weight:500;white-space:nowrap;letter-spacing:normal;color:#fff;background-color:#212121;'&gt;@FTeixeira&lt;/div&gt;');</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F62" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
